--- a/UAT_Excel_Reports/Promo Bundle_UAT.xlsx
+++ b/UAT_Excel_Reports/Promo Bundle_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,26 +496,39 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>--- NAVIGATION TO CREATE PROMOTIONS PAGE ---</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C.1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to the 'Create Promotions' page by entering the specified URL in the browser.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/create-promotions")`</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>C.1</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the 'Create Promotions' page by entering the specified URL in the browser.</t>
+          <t>Click on the 'Name' input field to begin entering the promotion event name.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/create-promotions")`</t>
+          <t>`page.get_by_test_id("promotionEventName").click()`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -523,26 +536,39 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>--- PROMOTION EVENT DETAILS INPUT ---</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>D.2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Enter the promotion event name 'rh--1137-0904' into the 'Name' input field.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotionEventName").fill("rh--1137-0904")`</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Name' input field to begin entering the promotion event name.</t>
+          <t>Click on the 'Description' input field to begin entering the promotion event description.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventName").click()`</t>
+          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -552,17 +578,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>D.2</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Enter the promotion event name 'rh--1137-0904' into the 'Name' input field.</t>
+          <t>Enter the promotion event description 'PROMO BUNDLE TEST 2' into the 'Description' input field.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventName").fill("rh--1137-0904")`</t>
+          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO BUNDLE TEST 2")`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -572,17 +598,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>D.3</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Description' input field to begin entering the promotion event description.</t>
+          <t>Click on the 'Start Date' field to open the date picker.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
+          <t>`page.get_by_test_id("startDate").click()`</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
@@ -592,17 +618,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Enter the promotion event description 'PROMO BUNDLE TEST 2' into the 'Description' input field.</t>
+          <t>From the date picker, select the 16th day of the month as the start date.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO BUNDLE TEST 2")`</t>
+          <t>`page.get_by_text("16").click()`</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -610,26 +636,39 @@
       <c r="F9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>--- DATE SELECTION ---</t>
-        </is>
-      </c>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>E.3</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'End Date' field to open the date picker.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("endDate").click()`</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Start Date' field to open the date picker.</t>
+          <t>From the date picker, select the 23rd day of the month as the end date.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("startDate").click()`</t>
+          <t>`page.get_by_text("23", exact=True).click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -639,17 +678,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>E.2</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>From the date picker, select the 16th day of the month as the start date.</t>
+          <t>Click on the 'ASAP Pricing' checkbox to enable this option under 'Additional Considerations'.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("16").click()`</t>
+          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
@@ -659,17 +698,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>E.3</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'End Date' field to open the date picker.</t>
+          <t>Click on the 'Select Locations' textbox to open the location selection panel.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("endDate").click()`</t>
+          <t>`page.get_by_role("textbox", name="Select Locations").click()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -679,17 +718,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>From the date picker, select the 23rd day of the month as the end date.</t>
+          <t>Click on 'Hierarchy' in the location selection panel to expand the hierarchy options.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("23", exact=True).click()`</t>
+          <t>`page.locator("#SideFilterlocationhierarchyId").get_by_text("Hierarchy").click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -697,26 +736,39 @@
       <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>--- ADDITIONAL CONSIDERATIONS AND LOCATION SELECTION ---</t>
-        </is>
-      </c>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>F.4</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Select 'Region' from the hierarchy options.</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Region", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>F.5</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'ASAP Pricing' checkbox to enable this option under 'Additional Considerations'.</t>
+          <t>Select the 'JPN' radio button to filter locations by the Japan region.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
+          <t>`page.get_by_role("radio", name="JPN").check()`</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -726,17 +778,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Select Locations' textbox to open the location selection panel.</t>
+          <t>Click on 'Price Zone Type' to expand the price zone type options.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Select Locations").click()`</t>
+          <t>`page.get_by_text("Price Zone Type").click()`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -746,17 +798,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Hierarchy' in the location selection panel to expand the hierarchy options.</t>
+          <t>Select the first checkbox under 'Price Zone Type' (e.g., 'Select All').</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#SideFilterlocationhierarchyId").get_by_text("Hierarchy").click()`</t>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").first.click()`</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -766,17 +818,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>F.8</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Select 'Region' from the hierarchy options.</t>
+          <t>Click on 'Price Zone' to expand the price zone options.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Region", exact=True).click()`</t>
+          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -786,17 +838,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F.5</t>
+          <t>F.9</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Select the 'JPN' radio button to filter locations by the Japan region.</t>
+          <t>Select a specific price zone checkbox (e.g., 'Collection').</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("radio", name="JPN").check()`</t>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -806,17 +858,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.10</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone Type' to expand the price zone type options.</t>
+          <t>Click on the 'Apply Filters' button to apply the selected location and price zone filters.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone Type").click()`</t>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -826,17 +878,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Select the first checkbox under 'Price Zone Type' (e.g., 'Select All').</t>
+          <t>Click on the 'Select Products' textbox to open the product selection panel.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").first.click()`</t>
+          <t>`page.get_by_role("textbox", name="Select Products").click()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -846,17 +898,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F.8</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone' to expand the price zone options.</t>
+          <t>Click on 'Hierarchy' in the product selection panel to expand the hierarchy options.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
+          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -866,17 +918,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>F.9</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Select a specific price zone checkbox (e.g., 'Collection').</t>
+          <t>Click on 'Style Color' in the hierarchy options to filter products by style color.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+          <t>`page.get_by_text("Style Color").click()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -886,17 +938,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F.10</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply Filters' button to apply the selected location and price zone filters.</t>
+          <t>Click on 'Style Color' again to ensure the filter is selected.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+          <t>`page.get_by_text("Style Color").click()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -904,26 +956,39 @@
       <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>--- PRODUCT SELECTION ---</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>G.5</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Select the first checkbox under 'Style Color' (e.g., 'Select All') to include all style colors.</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper").click()`</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Select Products' textbox to open the product selection panel.</t>
+          <t>Select a specific style color checkbox (e.g., '-2C8-01J999') to include it in the selection.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Select Products").click()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; div:nth-child(2) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -933,17 +998,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>G.7</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Hierarchy' in the product selection panel to expand the hierarchy options.</t>
+          <t>Click on the first unchecked checkbox to include another style color in the selection.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
+          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -953,17 +1018,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>G.8</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Style Color' in the hierarchy options to filter products by style color.</t>
+          <t>Click on the first unchecked checkbox again to ensure it is selected.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Style Color").click()`</t>
+          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
@@ -973,17 +1038,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>G.9</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Style Color' again to ensure the filter is selected.</t>
+          <t>Click on a specific product (e.g., '101AKB0201') to include it in the selection.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Style Color").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^101AKB0201$")).click()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -993,17 +1058,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>G.10</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Select the first checkbox under 'Style Color' (e.g., 'Select All') to include all style colors.</t>
+          <t>Click on the 'Apply Filters' button to apply the selected product filters.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper").click()`</t>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1013,17 +1078,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Select a specific style color checkbox (e.g., '-2C8-01J999') to include it in the selection.</t>
+          <t>Click on the dropdown menu under 'Set Optimization Objective' to view the available optimization options.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; div:nth-child(2) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1033,17 +1098,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Click on the first unchecked checkbox to include another style color in the selection.</t>
+          <t>Select 'Optimize for Margin Revenue' from the dropdown menu to set it as the optimization objective.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
+          <t>`page.get_by_text("Optimize for Margin Revenue").click()`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1053,17 +1118,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>G.8</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Click on the first unchecked checkbox again to ensure it is selected.</t>
+          <t>Click on the 'Next Promo Recommendations' button to proceed to the summary page.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1073,17 +1138,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>G.9</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Click on a specific product (e.g., '101AKB0201') to include it in the selection.</t>
+          <t>Click on the 'Show More' button to expand additional details in the summary section.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^101AKB0201$")).click()`</t>
+          <t>`page.get_by_test_id("summary-show-more-button").click()`</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1093,17 +1158,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>G.10</t>
+          <t>H.5</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply Filters' button to apply the selected product filters.</t>
+          <t>Click on the 'Available Products' tab to view the list of products included in the promotion.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+          <t>`page.get_by_text("Available Products").click()`</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1111,26 +1176,39 @@
       <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>--- OPTIMIZATION OBJECTIVE AND SUMMARY NAVIGATION ---</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>H.6</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Next Promo Recommendations' button again to finalize and proceed.</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown menu under 'Set Optimization Objective' to view the available optimization options.</t>
+          <t>Click on the first dropdown caret to expand the options for defining promotion groups.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
+          <t>`page.locator(".dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1140,17 +1218,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Select 'Optimize for Margin Revenue' from the dropdown menu to set it as the optimization objective.</t>
+          <t>Select the fourth option from the dropdown to choose a specific group configuration.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Optimize for Margin Revenue").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1160,17 +1238,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next Promo Recommendations' button to proceed to the summary page.</t>
+          <t>Click on the first element with the 'flex-grow-1' class to proceed with the group selection.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.locator(".flex-grow-1").first.click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1180,17 +1258,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Show More' button to expand additional details in the summary section.</t>
+          <t>Click on the 'Edit Group Name' button to modify the name of the selected group.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("summary-show-more-button").click()`</t>
+          <t>`page.get_by_test_id("group-name-edit-btn").click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1200,17 +1278,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>H.5</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Available Products' tab to view the list of products included in the promotion.</t>
+          <t>Fill in the group name field with 'Watch' to name the group.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Available Products").click()`</t>
+          <t>`page.get_by_test_id("name").fill("Watch")`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1220,17 +1298,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>I.6</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next Promo Recommendations' button again to finalize and proceed.</t>
+          <t>Click on the 'Buy 1 0 Eligible Products Selected Add' button to add eligible products to the group.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.get_by_text("Buy 1 0 Eligible Products Selected Add").click()`</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1238,26 +1316,39 @@
       <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>--- PROMOTION GROUP CONFIGURATION ---</t>
-        </is>
-      </c>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>I.7</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Add Group' button to create a new group.</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("group-add").click()`</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>I.8</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown caret to expand the options for defining promotion groups.</t>
+          <t>Click on the 'Product IDs' field to input product identifiers for the group.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".dropdown-caret").first.click()`</t>
+          <t>`page.get_by_test_id("product-ids").click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1267,17 +1358,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>I.9</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Select the fourth option from the dropdown to choose a specific group configuration.</t>
+          <t>Fill in the 'Product IDs' field with the specified product IDs, separated by new lines.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
+          <t>`page.get_by_test_id("product-ids").fill("005DKI0041\n100DKX5271\n100DKX534704\n101AKB0201")`</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1287,17 +1378,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>I.10</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element with the 'flex-grow-1' class to proceed with the group selection.</t>
+          <t>Click on the 'Save' button to save the group configuration.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".flex-grow-1").first.click()`</t>
+          <t>`page.get_by_test_id("save").click()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1307,17 +1398,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Edit Group Name' button to modify the name of the selected group.</t>
+          <t>Click on the 'Add Value' textbox to input a value for the promotion.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("group-name-edit-btn").click()`</t>
+          <t>`page.get_by_role("textbox", name="Add Value").click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1327,17 +1418,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Fill in the group name field with 'Watch' to name the group.</t>
+          <t>Fill in the 'Add Value' textbox with '35' to set the promotion value.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("name").fill("Watch")`</t>
+          <t>`page.get_by_role("textbox", name="Add Value").fill("35")`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1347,17 +1438,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>I.6</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Buy 1 0 Eligible Products Selected Add' button to add eligible products to the group.</t>
+          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Buy 1 0 Eligible Products Selected Add").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1367,17 +1458,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>I.7</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Add Group' button to create a new group.</t>
+          <t>Click on 'Price Zone Adjustment' to navigate to the section for adjusting price zones.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("group-add").click()`</t>
+          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1387,17 +1478,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>I.8</t>
+          <t>J.5</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product IDs' field to input product identifiers for the group.</t>
+          <t>Click on the '#attribute_value' field to select it for input.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("product-ids").click()`</t>
+          <t>`page.locator("#attribute_value").click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1407,17 +1498,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>I.9</t>
+          <t>J.6</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Fill in the 'Product IDs' field with the specified product IDs, separated by new lines.</t>
+          <t>Fill in the '#attribute_value' field with '40' to set the adjustment value.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("product-ids").fill("005DKI0041\n100DKX5271\n100DKX534704\n101AKB0201")`</t>
+          <t>`page.locator("#attribute_value").fill("40")`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1427,17 +1518,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>I.10</t>
+          <t>J.7</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Save' button to save the group configuration.</t>
+          <t>Click on the 'Apply' button to save and apply the price zone adjustment.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("save").click()`</t>
+          <t>`page.get_by_test_id("replicate-apply").click()`</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
@@ -1445,26 +1536,39 @@
       <c r="F54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>--- PROMOTION VALUE AND PRICE ZONE ADJUSTMENT ---</t>
-        </is>
-      </c>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>K.1</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Submit All for Approval' button to initiate the submission of the promotion for approval.</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Submit All for Approval").click()`</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Add Value' textbox to input a value for the promotion.</t>
+          <t>Confirm the submission by clicking the 'Yes, Submit' button in the confirmation modal.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Add Value").click()`</t>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1474,17 +1578,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Fill in the 'Add Value' textbox with '35' to set the promotion value.</t>
+          <t>Click on the 'Close' button to close the submission confirmation modal.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Add Value").fill("35")`</t>
+          <t>`page.get_by_role("button", name="Close").click()`</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1494,17 +1598,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>J.3</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
+          <t>Click on the 'Actions' button to open the actions menu.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1514,17 +1618,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>J.4</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone Adjustment' to navigate to the section for adjusting price zones.</t>
+          <t>Select 'Approve' from the actions menu to approve the promotion.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
+          <t>`page.get_by_text("Approve", exact=True).click()`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1534,17 +1638,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>K.6</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Click on the '#attribute_value' field to select it for input.</t>
+          <t>Confirm the approval by clicking the 'Confirm' button in the confirmation modal.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#attribute_value").click()`</t>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -1554,17 +1658,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>K.7</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Fill in the '#attribute_value' field with '40' to set the adjustment value.</t>
+          <t>Click on the 'Actions' button again to open the actions menu.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#attribute_value").fill("40")`</t>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1574,17 +1678,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>J.7</t>
+          <t>K.8</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to save and apply the price zone adjustment.</t>
+          <t>Select 'Reject' from the actions menu to reject the promotion.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("replicate-apply").click()`</t>
+          <t>`page.get_by_text("Reject").click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1592,26 +1696,39 @@
       <c r="F62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>--- SUBMISSION AND APPROVAL WORKFLOW ---</t>
-        </is>
-      </c>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>K.9</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the rejection by clicking the 'Confirm' button in the confirmation modal.</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>K.10</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Submit All for Approval' button to initiate the submission of the promotion for approval.</t>
+          <t>Click on the 'Actions' button again to open the actions menu.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Submit All for Approval").click()`</t>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1621,17 +1738,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>K.11</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Confirm the submission by clicking the 'Yes, Submit' button in the confirmation modal.</t>
+          <t>Select 'Withdraw' from the actions menu to withdraw the promotion.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.get_by_text("Withdraw", exact=True).click()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1641,17 +1758,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>K.12</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Close' button to close the submission confirmation modal.</t>
+          <t>Confirm the withdrawal by clicking the 'Confirm' button in the confirmation modal.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Close").click()`</t>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1661,17 +1778,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>L.1</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Actions' button to open the actions menu.</t>
+          <t>Click on the 'Next' button in the promotion creation flow to proceed to the next step.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1681,17 +1798,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>L.2</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Select 'Approve' from the actions menu to approve the promotion.</t>
+          <t>Close the current page to end the session for this specific tab or window.</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Approve", exact=True).click()`</t>
+          <t>`page.close()`</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -1701,17 +1818,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>K.6</t>
+          <t>L.3</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Confirm the approval by clicking the 'Confirm' button in the confirmation modal.</t>
+          <t>Close the browser context to clean up resources associated with this context.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`context.close()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1721,223 +1838,26 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>L.4</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Actions' button again to open the actions menu.</t>
+          <t>Close the browser to terminate the entire browser session.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`browser.close()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr"/>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>K.8</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Select 'Reject' from the actions menu to reject the promotion.</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Reject").click()`</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>K.9</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Confirm the rejection by clicking the 'Confirm' button in the confirmation modal.</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>K.10</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Actions' button again to open the actions menu.</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>K.11</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Select 'Withdraw' from the actions menu to withdraw the promotion.</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Withdraw", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>K.12</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Confirm the withdrawal by clicking the 'Confirm' button in the confirmation modal.</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>--- FINAL STEPS AND CLEANUP ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>L.1</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Next' button in the promotion creation flow to proceed to the next step.</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>L.2</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Close the current page to end the session for this specific tab or window.</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>`page.close()`</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>L.3</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Close the browser context to clean up resources associated with this context.</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>`context.close()`</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>L.4</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Close the browser to terminate the entire browser session.</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>`browser.close()`</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UAT_Excel_Reports/Promo Bundle_UAT.xlsx
+++ b/UAT_Excel_Reports/Promo Bundle_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,39 +496,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>C.1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Navigate to the 'Create Promotions' page by entering the specified URL in the browser.</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/create-promotions")`</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>--- NAVIGATION TO CREATE PROMOTIONS PAGE ---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>C.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Name' input field to begin entering the promotion event name.</t>
+          <t>Navigate to the 'Create Promotions' page by entering the specified URL in the browser.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventName").click()`</t>
+          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/create-promotions")`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -536,39 +523,26 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>D.2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Enter the promotion event name 'rh--1137-0904' into the 'Name' input field.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("promotionEventName").fill("rh--1137-0904")`</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>--- PROMOTION EVENT DETAILS INPUT ---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>D.3</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Description' input field to begin entering the promotion event description.</t>
+          <t>Click on the 'Name' input field to begin entering the promotion event name.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
+          <t>`page.get_by_test_id("promotionEventName").click()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -578,17 +552,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>D.2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Enter the promotion event description 'PROMO BUNDLE TEST 2' into the 'Description' input field.</t>
+          <t>Enter the promotion event name 'rh--1137-0904' into the 'Name' input field.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO BUNDLE TEST 2")`</t>
+          <t>`page.get_by_test_id("promotionEventName").fill("rh--1137-0904")`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -598,17 +572,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Start Date' field to open the date picker.</t>
+          <t>Click on the 'Description' input field to begin entering the promotion event description.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("startDate").click()`</t>
+          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
@@ -618,17 +592,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>E.2</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>From the date picker, select the 16th day of the month as the start date.</t>
+          <t>Enter the promotion event description 'PROMO BUNDLE TEST 2' into the 'Description' input field.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("16").click()`</t>
+          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO BUNDLE TEST 2")`</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -636,39 +610,26 @@
       <c r="F9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>E.3</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'End Date' field to open the date picker.</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("endDate").click()`</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>--- DATE SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>From the date picker, select the 23rd day of the month as the end date.</t>
+          <t>Click on the 'Start Date' field to open the date picker.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("23", exact=True).click()`</t>
+          <t>`page.get_by_test_id("startDate").click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -678,17 +639,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'ASAP Pricing' checkbox to enable this option under 'Additional Considerations'.</t>
+          <t>From the date picker, select the 16th day of the month as the start date.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
+          <t>`page.get_by_text("16").click()`</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
@@ -698,17 +659,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Select Locations' textbox to open the location selection panel.</t>
+          <t>Click on the 'End Date' field to open the date picker.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Select Locations").click()`</t>
+          <t>`page.get_by_test_id("endDate").click()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -718,17 +679,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Hierarchy' in the location selection panel to expand the hierarchy options.</t>
+          <t>From the date picker, select the 23rd day of the month as the end date.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#SideFilterlocationhierarchyId").get_by_text("Hierarchy").click()`</t>
+          <t>`page.get_by_text("23", exact=True).click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -736,39 +697,26 @@
       <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>F.4</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Select 'Region' from the hierarchy options.</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Region", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>--- ADDITIONAL CONSIDERATIONS AND LOCATION SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>F.5</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Select the 'JPN' radio button to filter locations by the Japan region.</t>
+          <t>Click on the 'ASAP Pricing' checkbox to enable this option under 'Additional Considerations'.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("radio", name="JPN").check()`</t>
+          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -778,17 +726,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone Type' to expand the price zone type options.</t>
+          <t>Click on the 'Select Locations' textbox to open the location selection panel.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone Type").click()`</t>
+          <t>`page.get_by_role("textbox", name="Select Locations").click()`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -798,17 +746,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Select the first checkbox under 'Price Zone Type' (e.g., 'Select All').</t>
+          <t>Click on 'Hierarchy' in the location selection panel to expand the hierarchy options.</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").first.click()`</t>
+          <t>`page.locator("#SideFilterlocationhierarchyId").get_by_text("Hierarchy").click()`</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -818,17 +766,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F.8</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone' to expand the price zone options.</t>
+          <t>Select 'Region' from the hierarchy options.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
+          <t>`page.get_by_text("Region", exact=True).click()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -838,17 +786,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F.9</t>
+          <t>F.5</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Select a specific price zone checkbox (e.g., 'Collection').</t>
+          <t>Select the 'JPN' radio button to filter locations by the Japan region.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("radio", name="JPN").check()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -858,17 +806,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>F.10</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply Filters' button to apply the selected location and price zone filters.</t>
+          <t>Click on 'Price Zone Type' to expand the price zone type options.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+          <t>`page.get_by_text("Price Zone Type").click()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -878,17 +826,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Select Products' textbox to open the product selection panel.</t>
+          <t>Select the first checkbox under 'Price Zone Type' (e.g., 'Select All').</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Select Products").click()`</t>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").first.click()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -898,17 +846,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>F.8</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Hierarchy' in the product selection panel to expand the hierarchy options.</t>
+          <t>Click on 'Price Zone' to expand the price zone options.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
+          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -918,17 +866,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>F.9</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Style Color' in the hierarchy options to filter products by style color.</t>
+          <t>Select a specific price zone checkbox (e.g., 'Collection').</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Style Color").click()`</t>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -938,17 +886,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>F.10</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Style Color' again to ensure the filter is selected.</t>
+          <t>Click on the 'Apply Filters' button to apply the selected location and price zone filters.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Style Color").click()`</t>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -956,39 +904,26 @@
       <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>G.5</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Select the first checkbox under 'Style Color' (e.g., 'Select All') to include all style colors.</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper").click()`</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCT SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Select a specific style color checkbox (e.g., '-2C8-01J999') to include it in the selection.</t>
+          <t>Click on the 'Select Products' textbox to open the product selection panel.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; div:nth-child(2) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("textbox", name="Select Products").click()`</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -998,17 +933,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Click on the first unchecked checkbox to include another style color in the selection.</t>
+          <t>Click on 'Hierarchy' in the product selection panel to expand the hierarchy options.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
+          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1018,17 +953,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>G.8</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Click on the first unchecked checkbox again to ensure it is selected.</t>
+          <t>Click on 'Style Color' in the hierarchy options to filter products by style color.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
+          <t>`page.get_by_text("Style Color").click()`</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
@@ -1038,17 +973,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.9</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Click on a specific product (e.g., '101AKB0201') to include it in the selection.</t>
+          <t>Click on 'Style Color' again to ensure the filter is selected.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^101AKB0201$")).click()`</t>
+          <t>`page.get_by_text("Style Color").click()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -1058,17 +993,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>G.10</t>
+          <t>G.5</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply Filters' button to apply the selected product filters.</t>
+          <t>Select the first checkbox under 'Style Color' (e.g., 'Select All') to include all style colors.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1078,17 +1013,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown menu under 'Set Optimization Objective' to view the available optimization options.</t>
+          <t>Select a specific style color checkbox (e.g., '-2C8-01J999') to include it in the selection.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; div:nth-child(2) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1098,17 +1033,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>G.7</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Select 'Optimize for Margin Revenue' from the dropdown menu to set it as the optimization objective.</t>
+          <t>Click on the first unchecked checkbox to include another style color in the selection.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Optimize for Margin Revenue").click()`</t>
+          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1118,17 +1053,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>G.8</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next Promo Recommendations' button to proceed to the summary page.</t>
+          <t>Click on the first unchecked checkbox again to ensure it is selected.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1138,17 +1073,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>G.9</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Show More' button to expand additional details in the summary section.</t>
+          <t>Click on a specific product (e.g., '101AKB0201') to include it in the selection.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("summary-show-more-button").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^101AKB0201$")).click()`</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1158,17 +1093,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>H.5</t>
+          <t>G.10</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Available Products' tab to view the list of products included in the promotion.</t>
+          <t>Click on the 'Apply Filters' button to apply the selected product filters.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Available Products").click()`</t>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1176,39 +1111,26 @@
       <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>H.6</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Next Promo Recommendations' button again to finalize and proceed.</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>--- OPTIMIZATION OBJECTIVE AND SUMMARY NAVIGATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown caret to expand the options for defining promotion groups.</t>
+          <t>Click on the dropdown menu under 'Set Optimization Objective' to view the available optimization options.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".dropdown-caret").first.click()`</t>
+          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1218,17 +1140,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Select the fourth option from the dropdown to choose a specific group configuration.</t>
+          <t>Select 'Optimize for Margin Revenue' from the dropdown menu to set it as the optimization objective.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
+          <t>`page.get_by_text("Optimize for Margin Revenue").click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1238,17 +1160,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element with the 'flex-grow-1' class to proceed with the group selection.</t>
+          <t>Click on the 'Next Promo Recommendations' button to proceed to the summary page.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".flex-grow-1").first.click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1258,17 +1180,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Edit Group Name' button to modify the name of the selected group.</t>
+          <t>Click on the 'Show More' button to expand additional details in the summary section.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("group-name-edit-btn").click()`</t>
+          <t>`page.get_by_test_id("summary-show-more-button").click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1278,17 +1200,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>H.5</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Fill in the group name field with 'Watch' to name the group.</t>
+          <t>Click on the 'Available Products' tab to view the list of products included in the promotion.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("name").fill("Watch")`</t>
+          <t>`page.get_by_text("Available Products").click()`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1298,17 +1220,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>I.6</t>
+          <t>H.6</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Buy 1 0 Eligible Products Selected Add' button to add eligible products to the group.</t>
+          <t>Click on the 'Next Promo Recommendations' button again to finalize and proceed.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Buy 1 0 Eligible Products Selected Add").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1316,39 +1238,26 @@
       <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>I.7</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Add Group' button to create a new group.</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("group-add").click()`</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>--- PROMOTION GROUP CONFIGURATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>I.8</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product IDs' field to input product identifiers for the group.</t>
+          <t>Click on the first dropdown caret to expand the options for defining promotion groups.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("product-ids").click()`</t>
+          <t>`page.locator(".dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1358,17 +1267,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>I.9</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Fill in the 'Product IDs' field with the specified product IDs, separated by new lines.</t>
+          <t>Select the fourth option from the dropdown to choose a specific group configuration.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("product-ids").fill("005DKI0041\n100DKX5271\n100DKX534704\n101AKB0201")`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1378,17 +1287,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>I.10</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Save' button to save the group configuration.</t>
+          <t>Click on the first element with the 'flex-grow-1' class to proceed with the group selection.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("save").click()`</t>
+          <t>`page.locator(".flex-grow-1").first.click()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1398,17 +1307,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Add Value' textbox to input a value for the promotion.</t>
+          <t>Click on the 'Edit Group Name' button to modify the name of the selected group.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Add Value").click()`</t>
+          <t>`page.get_by_test_id("group-name-edit-btn").click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1418,17 +1327,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Fill in the 'Add Value' textbox with '35' to set the promotion value.</t>
+          <t>Fill in the group name field with 'Watch' to name the group.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Add Value").fill("35")`</t>
+          <t>`page.get_by_test_id("name").fill("Watch")`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1438,17 +1347,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>J.3</t>
+          <t>I.6</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
+          <t>Click on the 'Buy 1 0 Eligible Products Selected Add' button to add eligible products to the group.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.get_by_text("Buy 1 0 Eligible Products Selected Add").click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1458,17 +1367,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>J.4</t>
+          <t>I.7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone Adjustment' to navigate to the section for adjusting price zones.</t>
+          <t>Click on the 'Add Group' button to create a new group.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
+          <t>`page.get_by_test_id("group-add").click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1478,17 +1387,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>I.8</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Click on the '#attribute_value' field to select it for input.</t>
+          <t>Click on the 'Product IDs' field to input product identifiers for the group.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#attribute_value").click()`</t>
+          <t>`page.get_by_test_id("product-ids").click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1498,17 +1407,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>I.9</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Fill in the '#attribute_value' field with '40' to set the adjustment value.</t>
+          <t>Fill in the 'Product IDs' field with the specified product IDs, separated by new lines.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#attribute_value").fill("40")`</t>
+          <t>`page.get_by_test_id("product-ids").fill("005DKI0041\n100DKX5271\n100DKX534704\n101AKB0201")`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1518,17 +1427,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>J.7</t>
+          <t>I.10</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to save and apply the price zone adjustment.</t>
+          <t>Click on the 'Save' button to save the group configuration.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("replicate-apply").click()`</t>
+          <t>`page.get_by_test_id("save").click()`</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
@@ -1536,39 +1445,26 @@
       <c r="F54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>K.1</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Submit All for Approval' button to initiate the submission of the promotion for approval.</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="Submit All for Approval").click()`</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>--- PROMOTION VALUE AND PRICE ZONE ADJUSTMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Confirm the submission by clicking the 'Yes, Submit' button in the confirmation modal.</t>
+          <t>Click on the 'Add Value' textbox to input a value for the promotion.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.get_by_role("textbox", name="Add Value").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1578,17 +1474,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Close' button to close the submission confirmation modal.</t>
+          <t>Fill in the 'Add Value' textbox with '35' to set the promotion value.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Close").click()`</t>
+          <t>`page.get_by_role("textbox", name="Add Value").fill("35")`</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1598,17 +1494,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Actions' button to open the actions menu.</t>
+          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1618,17 +1514,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Select 'Approve' from the actions menu to approve the promotion.</t>
+          <t>Click on 'Price Zone Adjustment' to navigate to the section for adjusting price zones.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Approve", exact=True).click()`</t>
+          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1638,17 +1534,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>K.6</t>
+          <t>J.5</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Confirm the approval by clicking the 'Confirm' button in the confirmation modal.</t>
+          <t>Click on the '#attribute_value' field to select it for input.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.locator("#attribute_value").click()`</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -1658,17 +1554,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>J.6</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Actions' button again to open the actions menu.</t>
+          <t>Fill in the '#attribute_value' field with '40' to set the adjustment value.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`page.locator("#attribute_value").fill("40")`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1678,17 +1574,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>K.8</t>
+          <t>J.7</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Select 'Reject' from the actions menu to reject the promotion.</t>
+          <t>Click on the 'Apply' button to save and apply the price zone adjustment.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reject").click()`</t>
+          <t>`page.get_by_test_id("replicate-apply").click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1696,39 +1592,26 @@
       <c r="F62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>K.9</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Confirm the rejection by clicking the 'Confirm' button in the confirmation modal.</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>--- SUBMISSION AND APPROVAL WORKFLOW ---</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>K.10</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Actions' button again to open the actions menu.</t>
+          <t>Click on the 'Submit All for Approval' button to initiate the submission of the promotion for approval.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`page.get_by_role("button", name="Submit All for Approval").click()`</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1738,17 +1621,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>K.11</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Select 'Withdraw' from the actions menu to withdraw the promotion.</t>
+          <t>Confirm the submission by clicking the 'Yes, Submit' button in the confirmation modal.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Withdraw", exact=True).click()`</t>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1758,17 +1641,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>K.12</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Confirm the withdrawal by clicking the 'Confirm' button in the confirmation modal.</t>
+          <t>Click on the 'Close' button to close the submission confirmation modal.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.get_by_role("button", name="Close").click()`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1778,17 +1661,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>L.1</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button in the promotion creation flow to proceed to the next step.</t>
+          <t>Click on the 'Actions' button to open the actions menu.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1798,17 +1681,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>L.2</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Close the current page to end the session for this specific tab or window.</t>
+          <t>Select 'Approve' from the actions menu to approve the promotion.</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>`page.close()`</t>
+          <t>`page.get_by_text("Approve", exact=True).click()`</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -1818,17 +1701,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>L.3</t>
+          <t>K.6</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Close the browser context to clean up resources associated with this context.</t>
+          <t>Confirm the approval by clicking the 'Confirm' button in the confirmation modal.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`context.close()`</t>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1838,26 +1721,223 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>L.4</t>
+          <t>K.7</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Close the browser to terminate the entire browser session.</t>
+          <t>Click on the 'Actions' button again to open the actions menu.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`browser.close()`</t>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>K.8</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Select 'Reject' from the actions menu to reject the promotion.</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Reject").click()`</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>K.9</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the rejection by clicking the 'Confirm' button in the confirmation modal.</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>K.10</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Actions' button again to open the actions menu.</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>K.11</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Select 'Withdraw' from the actions menu to withdraw the promotion.</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Withdraw", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>K.12</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the withdrawal by clicking the 'Confirm' button in the confirmation modal.</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>--- FINAL STEPS AND CLEANUP ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>L.1</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Next' button in the promotion creation flow to proceed to the next step.</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>L.2</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Close the current page to end the session for this specific tab or window.</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>`page.close()`</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>L.3</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Close the browser context to clean up resources associated with this context.</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>`context.close()`</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>L.4</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Close the browser to terminate the entire browser session.</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>`browser.close()`</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
